--- a/translations/portfolio_translations_review_deduplicated.xlsx
+++ b/translations/portfolio_translations_review_deduplicated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anoukfontaine/Desktop/Portfolio/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166B35A4-1752-C249-A6D6-8F32DFFE851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF0FCAF-2560-3549-9C30-6BC1464347CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hero" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="1340">
   <si>
     <t>data-i18n</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Services</t>
   </si>
   <si>
-    <t>Leistungen</t>
-  </si>
-  <si>
     <t>nav.work</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>This portfolio is currently shared with selected reviewers. Please enter the password to continue.</t>
   </si>
   <si>
-    <t>Dieses Portfolio wird derzeit mit ausgewählten Personen geteilt.&lt;br&gt;Bitte geben Sie das Passwort ein, um fortzufahren.</t>
-  </si>
-  <si>
     <t>Ce portfolio est actuellement partagé avec un nombre limité de personnes.&lt;br&gt;Veuillez saisir le mot de passe pour continuer.</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
     <t>As a UX Designer with a background in Business Intelligence and Data Visualization, I help organizations design and improve apps, dashboards and workflows so people can navigate complexity with confidence and spend more time on meaningful work.</t>
   </si>
   <si>
-    <t>Als UX Designerin, spezialisiert auf komplexe Produkte und Datenvisualisierung, unterstütze ich Organisationen dabei, Apps, Dashboards und Workflows so zu gestalten und weiterzuentwickeln, dass Menschen souverän darin navigieren können und mehr Zeit für das haben, was wirklich zählt..</t>
-  </si>
-  <si>
     <t>En tant que UX Designer spécialisée dans les produits complexes et la visualisation de données, j’aide les organisations à concevoir et améliorer leurs applications, dashboards et workflows afin que les utilisateurs puissent y naviguer avec aisance et consacrer davantage de temps à ce qui compte vraiment.</t>
   </si>
   <si>
@@ -199,9 +190,6 @@
     <t>View projects</t>
   </si>
   <si>
-    <t>Zu den Projekten</t>
-  </si>
-  <si>
     <t>Voir les projets</t>
   </si>
   <si>
@@ -253,9 +241,6 @@
     <t>UX audits</t>
   </si>
   <si>
-    <t>UX-Audits</t>
-  </si>
-  <si>
     <t>Audits UX</t>
   </si>
   <si>
@@ -289,9 +274,6 @@
     <t>UI design &amp; visual direction</t>
   </si>
   <si>
-    <t>UI Design &amp; visuelle Konzeption</t>
-  </si>
-  <si>
     <t>Design UI &amp; direction visuelle</t>
   </si>
   <si>
@@ -322,9 +304,6 @@
     <t>BI &amp; dashboard design</t>
   </si>
   <si>
-    <t>Dashboard &amp; BI Design</t>
-  </si>
-  <si>
     <t>Design de dashboards &amp; &lt;br/&gt;visualisations BI</t>
   </si>
   <si>
@@ -400,9 +379,6 @@
     <t>Stakeholder workshops</t>
   </si>
   <si>
-    <t>Prozessanalyse &amp; -optimierung</t>
-  </si>
-  <si>
     <t>Cartographie &amp; optimisation des processus</t>
   </si>
   <si>
@@ -508,9 +484,6 @@
     <t>Show, don't tell</t>
   </si>
   <si>
-    <t>Zeigen statt reden.</t>
-  </si>
-  <si>
     <t>Les actes plutôt que les mots.</t>
   </si>
   <si>
@@ -532,9 +505,6 @@
     <t>Read case study</t>
   </si>
   <si>
-    <t>Case Study ansehen</t>
-  </si>
-  <si>
     <t>Voir l’étude de cas</t>
   </si>
   <si>
@@ -553,9 +523,6 @@
     <t>A fragmented budget planning process required extensive manual work, while financial information was difficult for users to navigate, leading to low confidence in the data.</t>
   </si>
   <si>
-    <t>Ein fragmentierter Budgetplanungsprozess führte zu viel manueller Arbeit und machte es Nutzer:innen schwer, sich in den Finanzinformationen zurechtzufinden. Das schwächte das Vertrauen in die Daten.</t>
-  </si>
-  <si>
     <t>Un processus de planification budgétaire fragmenté générait beaucoup de travail manuel et rendait les informations financières difficiles à parcourir, ce qui réduisait la confiance dans les données.</t>
   </si>
   <si>
@@ -595,9 +562,6 @@
     <t>The education and training request workflow relied on manual checks, data transfers and error-prone calculations, creating unnecessary work for employees and HR.</t>
   </si>
   <si>
-    <t>Der Antragsprozess für Aus- und Weiterbildungen basierte auf manuellen Kontrollen, Datenübertragungen und fehleranfälligen Berechnungen. Das verursachte unnötigen Aufwand für Mitarbeitende und HR.</t>
-  </si>
-  <si>
     <t>Le processus de demande de formation et de perfectionnement reposait sur des contrôles manuels, des transferts de données et des calculs sujets aux erreurs, générant un travail inutile pour les collaborateurs comme pour les RH.</t>
   </si>
   <si>
@@ -607,9 +571,6 @@
     <t>A Power App guiding users through the full process, automating calculations and process steps from the initial request and approvals to cost participation and invoice submission.</t>
   </si>
   <si>
-    <t>Eine Power App, die Mitarbeitende und Führungskräfte durch den gesamten Prozess führt und Berechnungen sowie Prozessschritte automatisiert, von der ersten Antragstellung und den Genehmigungen über die Kostenbeteiligung bis zur Einreichung der Rechnung.</t>
-  </si>
-  <si>
     <t>Une Power App qui guide les collaborateurs et les responsables tout au long du processus, en automatisant les calculs et les différentes étapes, de la demande initiale et des validations jusqu’à la participation aux frais et au dépôt de la facture.</t>
   </si>
   <si>
@@ -631,9 +592,6 @@
     <t>Digital transformation has been a strategic priority within the Swiss Federal Administration for decades, yet many organizations still struggle to translate it into concrete action.</t>
   </si>
   <si>
-    <t>Die digitale Transformation ist seit Jahrzehnten eine strategische Priorität in der Schweizer Bundesverwaltung. Dennoch fällt es vielen Organisationen weiterhin schwer, daraus konkrete Massnahmen abzuleiten.</t>
-  </si>
-  <si>
     <t>La transformation numérique est une priorité stratégique de l’administration fédérale suisse depuis des décennies. Pourtant, de nombreuses organisations peinent encore à la traduire en actions concrètes.</t>
   </si>
   <si>
@@ -667,9 +625,6 @@
     <t>What people say</t>
   </si>
   <si>
-    <t>Was andere sagen</t>
-  </si>
-  <si>
     <t>Ce qu’on dit de mon travail</t>
   </si>
   <si>
@@ -691,9 +646,6 @@
     <t>solution-oriented</t>
   </si>
   <si>
-    <t>lösungsorientierten Art</t>
-  </si>
-  <si>
     <t>orientée solutions</t>
   </si>
   <si>
@@ -703,9 +655,6 @@
     <t>bridges the gap between business stakeholders and developers</t>
   </si>
   <si>
-    <t>zwischen Fachseite und Entwicklern</t>
-  </si>
-  <si>
     <t>le lien entre les métiers et les développeurs</t>
   </si>
   <si>
@@ -715,9 +664,6 @@
     <t>commitment to quality</t>
   </si>
   <si>
-    <t>Qualitätsanspruch</t>
-  </si>
-  <si>
     <t>exigence de qualité</t>
   </si>
   <si>
@@ -727,9 +673,6 @@
     <t>flexibility and dedication</t>
   </si>
   <si>
-    <t>ihrer Flexibilität und ihrem Engagement</t>
-  </si>
-  <si>
     <t>sa flexibilité et son engagement</t>
   </si>
   <si>
@@ -793,9 +736,6 @@
     <t>testimonials.items.aaron.context</t>
   </si>
   <si>
-    <t>Ländercockpit · Dashboard-Design</t>
-  </si>
-  <si>
     <t>Country Cockpit · Design de dashboard</t>
   </si>
   <si>
@@ -820,18 +760,12 @@
     <t>testimonials.items.aaron.role</t>
   </si>
   <si>
-    <t>Projektleiter, Bilaterale Wirtschaftsbeziehungen</t>
-  </si>
-  <si>
     <t>Chef de projet, Relations économiques bilatérales</t>
   </si>
   <si>
     <t>testimonials.items.daniel.context</t>
   </si>
   <si>
-    <t>Climate Cockpit · Dashboard-Design</t>
-  </si>
-  <si>
     <t>Climate Cockpit · Design de dashboard</t>
   </si>
   <si>
@@ -856,9 +790,6 @@
     <t>testimonials.items.daniel.role</t>
   </si>
   <si>
-    <t>Leiter Klimanetzwerk, SECO Wirtschaftliche Zusammenarbeit und Entwicklung</t>
-  </si>
-  <si>
     <t>Responsable du réseau climat, Coopération et développement économiques du SECO</t>
   </si>
   <si>
@@ -928,9 +859,6 @@
     <t>Ambassador, Head of Bilateral Economic Relations</t>
   </si>
   <si>
-    <t>Botschafterin, Leiterin Bilaterale Wirtschaftsbeziehungen</t>
-  </si>
-  <si>
     <t>Ambassadrice, cheffe des Relations économiques bilatérales</t>
   </si>
   <si>
@@ -958,9 +886,6 @@
     <t>City of Biel</t>
   </si>
   <si>
-    <t>Stadt Biel</t>
-  </si>
-  <si>
     <t>Ville de Bienne</t>
   </si>
   <si>
@@ -985,9 +910,6 @@
     <t>It's nice to meet you</t>
   </si>
   <si>
-    <t>Schön, dich kennenzulernen.</t>
-  </si>
-  <si>
     <t>Ravie de faire ta connaissance.</t>
   </si>
   <si>
@@ -997,9 +919,6 @@
     <t>Hello, visitor! I'm Anouk Fontaine, a UX Designer and BI Analyst at the State Secretariat for Economic Affairs (SECO) in Bern, Switzerland, where I help colleagues make better decisions through intuitive tools and interfaces. You can talk to me in French, (Swiss) German, English, or a mix of all three.</t>
   </si>
   <si>
-    <t>Hallo! Ich bin Anouk Fontaine, UX-Designerin und BI-Analystin beim Staatssekretariat für Wirtschaft (SECO) in Bern. Dort entwickle ich Tools und Interfaces, die meinen Kolleg:innen helfen, bessere Entscheidungen zu treffen. Du kannst mit mir auf Französisch, (Schweizer-)Deutsch, Englisch oder einfach in einer Mischung aus allem sprechen.</t>
-  </si>
-  <si>
     <t>Bonjour ! Je suis Anouk Fontaine, UX designeuse et analyste BI au Secrétariat d'État à l'économie (SECO), à Berne. J'y conçois des outils et des interfaces qui aident mes collègues à prendre de meilleures décisions au quotidien. Tu peux me parler en français, en (suisse) allemand, en anglais, ou dans un joyeux mélange des trois.</t>
   </si>
   <si>
@@ -1009,9 +928,6 @@
     <t>I've been designing for over 10 years.</t>
   </si>
   <si>
-    <t>Ich gestalte seit über 10 Jahren, auch wenn es nicht im Jobtitel stand.</t>
-  </si>
-  <si>
     <t>Je fais du design depuis plus de 10 ans, même si ça n'a pas toujours figuré dans mon titre.</t>
   </si>
   <si>
@@ -1021,9 +937,6 @@
     <t>I've worked across public administration, finance, human resources, and the hotel industry, giving me firsthand insight into a wide range of organizational challenges. My constant drive to make things easier for both my colleagues and myself has led me to apply UX design principles in every role I've held, whether UX was part of my job title or not. If you're curious about my journey, feel free to explore my detailed LinkedIn profile .</t>
   </si>
   <si>
-    <t>Ich habe in der öffentlichen Verwaltung, im Finanz- und Personalwesen sowie in der Hotellerie gearbeitet. Dadurch kenne ich ganz unterschiedliche organisatorische Herausforderungen aus erster Hand. Ich hatte schon immer den Drang, Dinge für meine Kolleg:innen und für mich selbst einfacher zu machen. Deshalb habe ich in jeder Rolle UX-Prinzipien angewendet, auch lange bevor UX Teil meines Jobtitels war. Wenn du neugierig auf meinen Werdegang bist, wirf gern einen Blick auf mein ausführliches &lt;a href="https://www.linkedin.com/in/anoukfontaine/" target="_blank"&gt;LinkedIn-Profil&lt;/a&gt;.</t>
-  </si>
-  <si>
     <t>J'ai travaillé dans l'administration publique, la finance, les ressources humaines et l'hôtellerie. Ces expériences m'ont permis de découvrir des réalités très différentes et de comprendre de nombreux défis organisationnels. J'ai toujours eu envie de simplifier les choses, autant pour mes collègues que pour moi-même. C'est ce qui m'a naturellement amenée à appliquer les principes du design UX dans chacun de mes postes, bien avant que l'UX fasse partie de mon intitulé. Si tu veux en savoir plus sur mon parcours, tu peux jeter un œil à mon &lt;a href="https://www.linkedin.com/in/anoukfontaine/" target="_blank"&gt;profil LinkedIn&lt;/a&gt;.</t>
   </si>
   <si>
@@ -1045,9 +958,6 @@
     <t>My Master's degree in Business Administration, combined with further education in UX design and data visualization, allows me to bridge business strategy, analytical thinking, and user experience.</t>
   </si>
   <si>
-    <t>Mein Master in Betriebswirtschaft und meine Weiterbildungen in UX-Design sowie Datenvisualisierung verbinden Unternehmensstrategie, analytisches Denken und User Experience. Das hilft mir, sowohl die Bedürfnisse von Nutzer:innen als auch die Ziele einer Organisation im Blick zu behalten.</t>
-  </si>
-  <si>
     <t>Mon master en économie d'entreprise, complété par des formations en design UX et en visualisation de données, me permet de faire le lien entre stratégie d'entreprise, analyse et expérience utilisateur.</t>
   </si>
   <si>
@@ -1069,9 +979,6 @@
     <t>I care about harmony, both in my designs and in the teams I work with. I’m curious about new technologies and eager to learn new tools, preferably by doing, from AI and web development tools to BI platforms and even music production software. I also believe that humour makes collaboration and problem-solving better.</t>
   </si>
   <si>
-    <t>Harmonie ist mir wichtig, sowohl in meinen Designs als auch in den Teams, mit denen ich zusammenarbeite. Ich tauche gerne in neue Themen ein und lerne am liebsten durch Ausprobieren. So ist auch dieses Portfolio entstanden: Selbstentwickelt von A bis Z, während ich mir die Webentwicklung Schritt für Schritt angeeignet habe. Ausserdem bin ich überzeugt: Eine Prise Humor macht die Zusammenarbeit und Problemlösung deutlich einfacher.</t>
-  </si>
-  <si>
     <t>L'harmonie est importante pour moi, autant dans ce que je conçois que dans les équipes avec lesquelles je travaille. J'adore apprendre de nouvelles choses, surtout en mettant directement les mains dans le cambouis. C'est d'ailleurs comme ça qu'est né ce portfolio : je l'ai développé de A à Z, en découvrant le développement web au fil de sa création. Et je suis convaincue qu'une bonne dose d'humour rend la collaboration et la résolution de problèmes bien plus agréables.</t>
   </si>
   <si>
@@ -1093,9 +1000,6 @@
     <t>In my free time, I'm also ah nuk, writing and recording songs in my bedroom, or outside taking snapshots.I'm also really into noodle soups. My favourite one is at Mondo in Bern, got any worthy contender?</t>
   </si>
   <si>
-    <t>In meiner Freizeit bin ich auch &lt;a href="https://bio.site/ah.nuk" target="_blank"&gt;ah nuk&lt;/a&gt;, schreibe und produziere Songs in meinem Schlafzimmer oder ziehe mit der Kamera los und mache &lt;a href="https://www.instagram.com/anoukfontaine?igsh=MWZzYjhjYzB1Y2p5aQ%3D%3D&amp;utm_source=qr" target="_blank"&gt;Schnappschüsse&lt;/a&gt;.&lt;br /&gt;Ausserdem liebe ich Nudelsuppen. Meine Lieblingssuppe gibt's im Mondo in Bern – kennst du einen würdigen Gegenkandidaten?</t>
-  </si>
-  <si>
     <t>Pendant mon temps libre, je suis aussi &lt;a href="https://bio.site/ah.nuk" target="_blank"&gt;ah nuk&lt;/a&gt;, j’écris et j’enregistre des chansons dans ma chambre. Sinon, on peut souvent me trouver dehors, appareil photo à la main, à capturer quelques &lt;a href="https://www.instagram.com/anoukfontaine?igsh=MWZzYjhjYzB1Y2p5aQ%3D%3D&amp;utm_source=qr" target="_blank"&gt;instants.&lt;/a&gt;.&lt;br /&gt; Je suis également une grande amatrice de soupes de nouilles. Ma préférée est celle de Mondo à Berne. Tu connais une adresse qui pourrait rivaliser ?</t>
   </si>
   <si>
@@ -1138,12 +1042,6 @@
     <t>contact.intro</t>
   </si>
   <si>
-    <t>Open to full-time opportunities, freelance collaborations and interesting conversations.</t>
-  </si>
-  <si>
-    <t>Offen für Festanstellungen, Freelancing und spannende Gespräche.</t>
-  </si>
-  <si>
     <t>Ouverte à un poste fixe, à des missions freelance et aux discussions intéressantes.</t>
   </si>
   <si>
@@ -1153,12 +1051,6 @@
     <t>Case Study - Yellow is the New Green</t>
   </si>
   <si>
-    <t>Fallstudie — Gelb ist das neue Grün</t>
-  </si>
-  <si>
-    <t>Étude de cas — Le jaune est le nouveau vert</t>
-  </si>
-  <si>
     <t>cs_shared.sidebar_overview</t>
   </si>
   <si>
@@ -1189,9 +1081,6 @@
     <t>Prozess</t>
   </si>
   <si>
-    <t>Processus</t>
-  </si>
-  <si>
     <t>cs_shared.sidebar_research</t>
   </si>
   <si>
@@ -1216,9 +1105,6 @@
     <t>03 Entwicklung</t>
   </si>
   <si>
-    <t>03 Dev</t>
-  </si>
-  <si>
     <t>cs_shared.sidebar_test</t>
   </si>
   <si>
@@ -1234,9 +1120,6 @@
     <t>05 Weiterentwickeln</t>
   </si>
   <si>
-    <t>05 Faire évoluer</t>
-  </si>
-  <si>
     <t>cs_shared.sidebar_product</t>
   </si>
   <si>
@@ -1286,12 +1169,6 @@
   </si>
   <si>
     <t>yellow.overview_note</t>
-  </si>
-  <si>
-    <t>Note: To protect internal information, the illustrations and mockups have been simplified. The main dashboard mockup is entirely fictional and is intended only to convey the general type and structure of the solution.</t>
-  </si>
-  <si>
-    <t>Hinweis: Zum Schutz interner Informationen wurden die Illustrationen und Mockups vereinfacht. Das zentrale Dashboard-Mockup ist vollständig fiktiv und soll lediglich einen Eindruck von der Art und Struktur der Lösung vermitteln.</t>
   </si>
   <si>
     <t>Remarque : afin de protéger les informations internes, les illustrations et les maquettes ont été simplifiées. La maquette principale du tableau de bord est entièrement fictive et sert uniquement à donner une idée générale du type et de la structure de la solution.</t>
@@ -3974,9 +3851,6 @@
     <t>Ein fragmentierter Budgetplanungsprozess verursachte hohen manuellen Aufwand. Gleichzeitig waren Informationen schwer auffindbar, was das Vertrauen in die Daten beeinträchtigte.</t>
   </si>
   <si>
-    <t>u</t>
-  </si>
-  <si>
     <t>Ein Finanzdashboard für die Planung und das Monitoring eines jährlichen Budgets von über CHF 400 Millionen reduzierte die manuelle Vorbereitungszeit um 90 % und erreichte bei den primären Nutzer eine Zufriedenheitsquote von 100 %.</t>
   </si>
   <si>
@@ -4050,6 +3924,129 @@
   </si>
   <si>
     <t>Hallo, mein Name ist Anouk Fontaine und ich bin UX-Designerin und BI-Analystin beim Staatssekretariat für Wirtschaft (SECO) in Bern, Schweiz. Ich unterstütze Kolleg:innen dabei, mit intuitiven Tools und Interfaces bessere Entscheidungen zu treffen. Du kannst mit mir auf Französisch, (Schweizer-) Deutsch, Englisch oder in einem Mix aus allen drei Sprachen sprechen.</t>
+  </si>
+  <si>
+    <t>Meine Arbeitserfahrung konnte ich in verschiedensten Bereichen sammeln, unter anderem in den Finanzen, im Personalwesen und in der Hotellerie, wo ich aus unterschiedlichen organisatorischen Herausforderungen lernen konnte. Der Drang, immer nach Möglichkeiten zu suchen, die Arbeit meiner Arbeitskolleg:innen und meine eigene zu vereinfachen und zu optimieren, hat dazu geführt, dass ich bereits in all meinen Jobs UX-Design-Prinzipien angewendet habe, auch wenn dies nicht in meinem Jobtitel stand. Mehr zu meinem Werdegang findest du in meinem &lt;a href="https://www.linkedin.com/in/anoukfontaine/" target="_blank"&gt;LinkedIn-Profil&lt;/a&gt;.</t>
+  </si>
+  <si>
+    <t>Ein Master in Betriebswirtschaft, kombiniert mit Weiterbildungen in UX Design und Datenvisualisierung, ermöglicht mir, Unternehmensstrategie mit analytischem Denken und User Experience zu verbinden.</t>
+  </si>
+  <si>
+    <t>Harmonie ist mir sehr wichtig, sei es in meinen Designs oder in der Zusammenarbeit im Team. Ausserdem begeistern mich neue Technologien, und die lerne ich am liebsten auch gleich durch Ausprobieren. Diese können von KI- und Webentwicklungstools über BI-Plattformen bis hin zu Musikproduktionssoftware reichen. Ich bin ausserdem überzeugt, dass Humor die Zusammenarbeit verbessert und hilft, bessere Lösungen zu finden.</t>
+  </si>
+  <si>
+    <t>In meiner Freizeit bin ich auch &lt;a href="https://bio.site/ah.nuk" target="_blank"&gt;ah nuk&lt;/a&gt;, schreibe und produziere Songs in meinem Schlafzimmer oder ich bin draussen am Landschaften verewigen.</t>
+  </si>
+  <si>
+    <t>Open to remote opportunities, freelance collaborations and interesting conversations.</t>
+  </si>
+  <si>
+    <t>Offen für Remote-Festanstellungen, Freelancing und spannende Gespräche.</t>
+  </si>
+  <si>
+    <t>Design ist seit 10 Jahren Teil meiner Arbeit.</t>
+  </si>
+  <si>
+    <t>Anouk Fontaine | UX Designeuse</t>
+  </si>
+  <si>
+    <t>En tant que UX Designer spécialisée dans les produits complexes et la visualisation de données, j’aide les organisations à concevoir et améliorer leurs applications, dashboards et workflows afin que les utilisateurs puissent y naviguer avec confiance et consacrer davantage de temps à ce qui compte vraiment.</t>
+  </si>
+  <si>
+    <t>Workshops pour stakeholders</t>
+  </si>
+  <si>
+    <t>Modélisation &amp; optimisation des processus</t>
+  </si>
+  <si>
+    <t>Projets phares</t>
+  </si>
+  <si>
+    <t>Au cœur de mon travail</t>
+  </si>
+  <si>
+    <t>Tableau de bord pour la planification financière</t>
+  </si>
+  <si>
+    <t>En savoir plus</t>
+  </si>
+  <si>
+    <t>Le problème</t>
+  </si>
+  <si>
+    <t>La solution</t>
+  </si>
+  <si>
+    <t>Un tableau de bord financier pour planifier et suivre un budget annuel de plus de CHF 400 millions réduit de 90% le travail manuel de préparation et atteint 100% de satisfaction chez les utilisateurs primaires.</t>
+  </si>
+  <si>
+    <t>Projekt - Gelb ist das neue Grün</t>
+  </si>
+  <si>
+    <t>Übersicht</t>
+  </si>
+  <si>
+    <t>Ergebnisse</t>
+  </si>
+  <si>
+    <t>Résultats</t>
+  </si>
+  <si>
+    <t>Vorgehen</t>
+  </si>
+  <si>
+    <t>Démarche</t>
+  </si>
+  <si>
+    <t>03 Bauen</t>
+  </si>
+  <si>
+    <t>04 Testen</t>
+  </si>
+  <si>
+    <t>05 Ausbauen</t>
+  </si>
+  <si>
+    <t>03 Construire</t>
+  </si>
+  <si>
+    <t>04 Tester</t>
+  </si>
+  <si>
+    <t>02 Designer</t>
+  </si>
+  <si>
+    <t>05 Enrichir</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>Projet - Le jaune est le nouveau vert</t>
+  </si>
+  <si>
+    <t>Ein fragmentierter, Budgetplanungsprozess verursachte hohen manuellen Aufwand. Gleichzeitig waren Informationen schwer auffindbar, was das Vertrauen in die Daten beeinträchtigte.</t>
+  </si>
+  <si>
+    <t>Ein fragmentierter, Excel-basierter Budgetplanungsprozess wird in ein interaktives Dashboard umgewandelt, das Entscheidungsträger dabei unterstützt, Daten zu verstehen, Zusammenhänge zu erkennen und bessere Entscheidungen zu treffen.</t>
+  </si>
+  <si>
+    <t>02 Designen</t>
+  </si>
+  <si>
+    <t>Transformation d’un processus de budgétisation financière basé sur Excel en un tableau de bord interactif aidant les responsables décisionnels à mieux comprendre les données, à identifier les tendances et à prendre de meilleures décisions en toute confiance.</t>
+  </si>
+  <si>
+    <t>Note: This project was completed as part of a permanent position. To protect internal information, identifying elements have been removed and fictional data has been used.</t>
+  </si>
+  <si>
+    <t>Hinweis: Dieses Projekt entstand im Rahmen einer Festanstellung. Zum Schutz interner Informationen wurden Daten wurden anonymisiert.</t>
+  </si>
+  <si>
+    <t>Hinweis: Dieses Projekt entstand im Rahmen einer Festanstellung. Zum Schutz interner Informationen wurden organisationsspezifische Elemente entfernt und fiktive Daten verwendet.</t>
+  </si>
+  <si>
+    <t>Remarque : Ce projet a été réalisé dans le cadre d'un emploi fixe. Afin de protéger les informations internes, les éléments propres à l’organisation ont été retirés et des données fictives ont été utilisées.</t>
   </si>
 </sst>
 </file>
@@ -4116,7 +4113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4131,6 +4128,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4361,13 +4361,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4378,38 +4378,38 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
@@ -4418,15 +4418,15 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -4435,21 +4435,21 @@
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>22</v>
@@ -4469,1595 +4469,1516 @@
         <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29">
       <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>1304</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="29">
       <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="57">
       <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>55</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1306</v>
+        <v>55</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>59</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1303</v>
+        <v>60</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1262</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1303</v>
+        <v>1262</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>1262</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1303</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1307</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>77</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1308</v>
+        <v>83</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1309</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1308</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>130</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>132</v>
+      <c r="E37" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>135</v>
+        <v>1308</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1311</v>
+        <v>150</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1310</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>12</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>1312</v>
+        <v>152</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1311</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>162</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>165</v>
+        <v>1312</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
         <v>1313</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>170</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>172</v>
+        <v>1314</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="43">
       <c r="A49" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1314</v>
+        <v>166</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>177</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>180</v>
+        <v>1315</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="43">
       <c r="A51" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>1316</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1315</v>
+        <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>183</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="43">
       <c r="A53" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>1317</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>191</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="43">
       <c r="A54" s="2" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>1318</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>195</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>198</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43">
       <c r="A56" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>1319</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>203</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="29">
       <c r="A57" s="2" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>1320</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>207</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>1325</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>215</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>1321</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>223</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>1322</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>227</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>1323</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>231</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>1324</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>235</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>238</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>249</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>253</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>1327</v>
-      </c>
+        <v>1284</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>257</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="85">
       <c r="A71" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>260</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>1328</v>
-      </c>
+        <v>1286</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>263</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>1329</v>
-      </c>
+        <v>1292</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>266</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1331</v>
-      </c>
+        <v>1288</v>
+      </c>
+      <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>269</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="57">
       <c r="A75" s="2" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>272</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>1332</v>
-      </c>
+        <v>1290</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>275</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="29">
       <c r="A77" s="2" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>1335</v>
-      </c>
+        <v>1291</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>278</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="29">
       <c r="A79" s="2" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>287</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>290</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>1327</v>
-      </c>
+        <v>1284</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>257</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="57">
       <c r="A83" s="2" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>1336</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>298</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>1337</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>302</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="29">
       <c r="A87" s="2" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>307</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>1338</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>312</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>315</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>1339</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="57">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="71">
       <c r="A92" s="2" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>323</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="71">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" s="2" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>1340</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="99">
+        <v>301</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="113">
       <c r="A94" s="2" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>333</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="57">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="43">
       <c r="A96" s="2" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>341</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="85">
       <c r="A98" s="2" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>347</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>349</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="99">
       <c r="A100" s="2" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>357</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>18</v>
@@ -6065,45 +5986,45 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="C103" s="2"/>
-      <c r="D103" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>371</v>
+        <v>338</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>1303</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>373</v>
+        <v>1304</v>
       </c>
     </row>
   </sheetData>
@@ -6113,14 +6034,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="4" width="75" customWidth="1"/>
+    <col min="2" max="6" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" customHeight="1">
+    <row r="1" spans="1:6" ht="27" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6131,1645 +6052,1951 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43">
+      <c r="A14" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="48">
+      <c r="A15" s="2" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="B15" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="57">
+      <c r="A17" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="43">
+      <c r="A19" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+    <row r="20" spans="1:6">
+      <c r="A20" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="57">
+      <c r="A21" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="29">
+      <c r="A22" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="43">
+      <c r="A24" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="43">
-      <c r="A14" s="2" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="43">
-      <c r="A15" s="2" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="29">
+      <c r="A26" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="57">
-      <c r="A17" s="2" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="29">
+      <c r="A28" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="29">
-      <c r="A19" s="2" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D19" s="2" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="29">
+      <c r="A30" s="2" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D20" s="2" t="s">
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="2" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="57">
-      <c r="A21" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D21" s="2" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="29">
+      <c r="A32" s="2" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="29">
-      <c r="A22" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="D22" s="2" t="s">
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D23" s="2" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="43">
+      <c r="A34" s="2" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="43">
-      <c r="A24" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D24" s="2" t="s">
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="2" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D25" s="2" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="29">
+      <c r="A36" s="2" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="29">
-      <c r="A26" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D26" s="2" t="s">
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="2" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D27" s="2" t="s">
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="2" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="29">
-      <c r="A28" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D28" s="2" t="s">
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="2" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D29" s="2" t="s">
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="2" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="29">
-      <c r="A30" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B31" s="2" t="s">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="29">
-      <c r="A32" s="2" t="s">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
+      <c r="E43" s="2"/>
+      <c r="F43" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="43">
-      <c r="A34" s="2" t="s">
+      <c r="E44" s="2"/>
+      <c r="F44" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B34" s="2" t="s">
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
+      <c r="E45" s="2"/>
+      <c r="F45" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B35" s="2" t="s">
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="29">
-      <c r="A36" s="2" t="s">
+      <c r="E46" s="2"/>
+      <c r="F46" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B36" s="2" t="s">
+    </row>
+    <row r="47" spans="1:6" ht="29">
+      <c r="A47" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
+      <c r="E47" s="2"/>
+      <c r="F47" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B37" s="2" t="s">
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2" t="s">
+      <c r="E48" s="2"/>
+      <c r="F48" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B38" s="2" t="s">
+    </row>
+    <row r="49" spans="1:6" ht="29">
+      <c r="A49" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="2" t="s">
+      <c r="E49" s="2"/>
+      <c r="F49" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B39" s="2" t="s">
+    </row>
+    <row r="50" spans="1:6" ht="29">
+      <c r="A50" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="2" t="s">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B40" s="2" t="s">
+    </row>
+    <row r="51" spans="1:6" ht="29">
+      <c r="A51" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="E51" s="2"/>
+      <c r="F51" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D41" s="2" t="s">
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="2" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C52" s="2"/>
+      <c r="D52" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D42" s="2" t="s">
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="2" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C53" s="2"/>
+      <c r="D53" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="E53" s="2"/>
+      <c r="F53" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D43" s="2" t="s">
+    </row>
+    <row r="54" spans="1:6" ht="29">
+      <c r="A54" s="2" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D44" s="2" t="s">
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="2" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D45" s="2" t="s">
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="2" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="E56" s="2"/>
+      <c r="F56" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D46" s="2" t="s">
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="2" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="29">
-      <c r="A47" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="E57" s="2"/>
+      <c r="F57" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D47" s="2" t="s">
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="2" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="E58" s="2"/>
+      <c r="F58" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D48" s="2" t="s">
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="2" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="29">
-      <c r="A49" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D49" s="2" t="s">
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="2" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="29">
-      <c r="A50" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C50" s="2" t="s">
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="29">
-      <c r="A51" s="2" t="s">
+      <c r="C61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B51" s="2" t="s">
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="C62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="2" t="s">
+    <row r="63" spans="1:6">
+      <c r="A63" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E63" s="2"/>
+      <c r="F63" s="2" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="2" t="s">
+    <row r="64" spans="1:6">
+      <c r="A64" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C64" s="2"/>
+      <c r="D64" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E64" s="2"/>
+      <c r="F64" s="2" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="29">
-      <c r="A54" s="2" t="s">
+    <row r="65" spans="1:6">
+      <c r="A65" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C65" s="2"/>
+      <c r="D65" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E65" s="2"/>
+      <c r="F65" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="2" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C66" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="C67" s="2"/>
+      <c r="D67" s="2" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="2" t="s">
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B56" s="2" t="s">
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="C68" s="2"/>
+      <c r="D68" s="2" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2" t="s">
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B57" s="2" t="s">
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="C69" s="2"/>
+      <c r="D69" s="2" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2" t="s">
+      <c r="E69" s="2"/>
+      <c r="F69" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B58" s="2" t="s">
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2" t="s">
+      <c r="E70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C71" s="2"/>
+      <c r="D71" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
+    <row r="72" spans="1:6">
+      <c r="A72" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="C72" s="2"/>
+      <c r="D72" s="2" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B61" s="2" t="s">
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
+      <c r="C73" s="2"/>
+      <c r="D73" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="E73" s="2"/>
+      <c r="F73" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="D62" s="2" t="s">
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="2" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="D63" s="2" t="s">
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="2" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C75" s="2"/>
+      <c r="D75" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="E75" s="2"/>
+      <c r="F75" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2" t="s">
+      <c r="C76" s="2"/>
+      <c r="D76" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="E76" s="2"/>
+      <c r="F76" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C65" s="2" t="s">
+    </row>
+    <row r="77" spans="1:6" ht="99">
+      <c r="A77" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C77" s="2"/>
+      <c r="D77" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B67" s="2" t="s">
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="C78" s="2"/>
+      <c r="D78" s="2" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2" t="s">
+      <c r="E78" s="2"/>
+      <c r="F78" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B79" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="C80" s="2"/>
+      <c r="D80" s="2" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2" t="s">
+      <c r="E80" s="2"/>
+      <c r="F80" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="B69" s="2" t="s">
+    </row>
+    <row r="81" spans="1:6" ht="99">
+      <c r="A81" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="2" t="s">
+      <c r="E81" s="2"/>
+      <c r="F81" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B70" s="2" t="s">
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="2" t="s">
+      <c r="C82" s="2"/>
+      <c r="D82" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="E82" s="2"/>
+      <c r="F82" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C71" s="2" t="s">
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="2" t="s">
+      <c r="C83" s="2"/>
+      <c r="D83" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="E83" s="2"/>
+      <c r="F83" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="C72" s="2" t="s">
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="2" t="s">
+      <c r="C84" s="2"/>
+      <c r="D84" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="E84" s="2"/>
+      <c r="F84" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C73" s="2" t="s">
+    </row>
+    <row r="85" spans="1:6" ht="43">
+      <c r="A85" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="2" t="s">
+      <c r="C85" s="2"/>
+      <c r="D85" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="E85" s="2"/>
+      <c r="F85" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C74" s="2" t="s">
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="2" t="s">
+      <c r="C86" s="2"/>
+      <c r="D86" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="E86" s="2"/>
+      <c r="F86" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="C75" s="2" t="s">
+    </row>
+    <row r="87" spans="1:6" ht="57">
+      <c r="A87" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="2" t="s">
+      <c r="B87" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C87" s="2"/>
+      <c r="D87" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="E87" s="2"/>
+      <c r="F87" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D76" s="2" t="s">
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="2" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="99">
-      <c r="A77" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C88" s="2"/>
+      <c r="D88" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D77" s="2" t="s">
+    </row>
+    <row r="89" spans="1:6" ht="43">
+      <c r="A89" s="2" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="E89" s="2"/>
+      <c r="F89" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="2" t="s">
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C90" s="2"/>
+      <c r="D90" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="E90" s="2"/>
+      <c r="F90" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="D80" s="2" t="s">
+    </row>
+    <row r="91" spans="1:6" ht="43">
+      <c r="A91" s="2" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="99">
-      <c r="A81" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C91" s="2"/>
+      <c r="D91" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="E91" s="2"/>
+      <c r="F91" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="D81" s="2" t="s">
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="2" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C92" s="2"/>
+      <c r="D92" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="E92" s="2"/>
+      <c r="F92" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="D82" s="2" t="s">
+    </row>
+    <row r="93" spans="1:6" ht="57">
+      <c r="A93" s="2" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C93" s="2"/>
+      <c r="D93" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="E93" s="2"/>
+      <c r="F93" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D83" s="2" t="s">
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="2" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C94" s="2"/>
+      <c r="D94" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="C95" s="2"/>
+      <c r="D95" s="2" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="43">
-      <c r="A85" s="2" t="s">
+      <c r="E95" s="2"/>
+      <c r="F95" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B85" s="2" t="s">
+    </row>
+    <row r="96" spans="1:6" ht="113">
+      <c r="A96" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="C96" s="2"/>
+      <c r="D96" s="2" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="2" t="s">
+      <c r="E96" s="2"/>
+      <c r="F96" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B86" s="2" t="s">
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="C97" s="2"/>
+      <c r="D97" s="2" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="57">
-      <c r="A87" s="2" t="s">
+      <c r="E97" s="2"/>
+      <c r="F97" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B87" s="2" t="s">
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="C98" s="2"/>
+      <c r="D98" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="2" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="2" t="s">
+      <c r="B99" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C99" s="2"/>
+      <c r="D99" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="E99" s="2"/>
+      <c r="F99" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="D88" s="2" t="s">
+    </row>
+    <row r="100" spans="1:6" ht="113">
+      <c r="A100" s="2" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="43">
-      <c r="A89" s="2" t="s">
+      <c r="B100" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C100" s="2"/>
+      <c r="D100" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="E100" s="2"/>
+      <c r="F100" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="D89" s="2" t="s">
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="2" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="2" t="s">
+      <c r="B101" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B102" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C102" s="2"/>
+      <c r="D102" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="E102" s="2"/>
+      <c r="F102" s="2" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="43">
-      <c r="A91" s="2" t="s">
+    <row r="103" spans="1:6">
+      <c r="A103" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B103" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C103" s="2"/>
+      <c r="D103" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="E103" s="2"/>
+      <c r="F103" s="2" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="2" t="s">
+    <row r="104" spans="1:6">
+      <c r="A104" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B104" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C104" s="2"/>
+      <c r="D104" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="E104" s="2"/>
+      <c r="F104" s="2" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="57">
-      <c r="A93" s="2" t="s">
+    <row r="105" spans="1:6">
+      <c r="A105" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B105" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C105" s="2"/>
+      <c r="D105" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E105" s="2"/>
+      <c r="F105" s="2" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="2" t="s">
+    <row r="106" spans="1:6">
+      <c r="A106" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B106" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="2" t="s">
+      <c r="C106" s="2"/>
+      <c r="D106" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="E106" s="2"/>
+      <c r="F106" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="C95" s="2" t="s">
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" ht="113">
-      <c r="A96" s="2" t="s">
+      <c r="C107" s="2"/>
+      <c r="D107" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="E107" s="2"/>
+      <c r="F107" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="C96" s="2" t="s">
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="2" t="s">
+      <c r="C108" s="2"/>
+      <c r="D108" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="E108" s="2"/>
+      <c r="F108" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="C97" s="2" t="s">
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="2" t="s">
+      <c r="C109" s="2"/>
+      <c r="D109" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="E109" s="2"/>
+      <c r="F109" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="2" t="s">
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B110" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C110" s="2"/>
+      <c r="D110" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="E110" s="2"/>
+      <c r="F110" s="2" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="113">
-      <c r="A100" s="2" t="s">
+    <row r="111" spans="1:6">
+      <c r="A111" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C111" s="2"/>
+      <c r="D111" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="E111" s="2"/>
+      <c r="F111" s="2" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="2" t="s">
+    <row r="112" spans="1:6" ht="71">
+      <c r="A112" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C112" s="2"/>
+      <c r="D112" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="E112" s="2"/>
+      <c r="F112" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D102" s="2" t="s">
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="2" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C113" s="2"/>
+      <c r="D113" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="E113" s="2"/>
+      <c r="F113" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="D103" s="2" t="s">
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="2" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C114" s="2"/>
+      <c r="D114" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="E114" s="2"/>
+      <c r="F114" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="D104" s="2" t="s">
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="2" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C115" s="2"/>
+      <c r="D115" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="E115" s="2"/>
+      <c r="F115" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="D105" s="2" t="s">
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="2" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C116" s="2"/>
+      <c r="D116" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="E116" s="2"/>
+      <c r="F116" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="D106" s="2" t="s">
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="2" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C117" s="2"/>
+      <c r="D117" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="E117" s="2"/>
+      <c r="F117" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="D107" s="2" t="s">
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="2" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="2" t="s">
+      <c r="B118" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C118" s="2"/>
+      <c r="D118" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="E118" s="2"/>
+      <c r="F118" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="71">
-      <c r="A112" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -7802,926 +8029,926 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>815</v>
+        <v>774</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>816</v>
+        <v>775</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>817</v>
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>818</v>
+        <v>777</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>820</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>821</v>
+        <v>780</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>822</v>
+        <v>781</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>823</v>
+        <v>782</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>823</v>
+        <v>782</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>824</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>825</v>
+        <v>784</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>826</v>
+        <v>785</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>827</v>
+        <v>786</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>828</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>829</v>
+        <v>788</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>830</v>
+        <v>789</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>831</v>
+        <v>790</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>832</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="43">
       <c r="A8" s="2" t="s">
-        <v>833</v>
+        <v>792</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>834</v>
+        <v>793</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>835</v>
+        <v>794</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>836</v>
+        <v>795</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="43">
       <c r="A9" s="2" t="s">
-        <v>837</v>
+        <v>796</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>838</v>
+        <v>797</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>839</v>
+        <v>798</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>840</v>
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="57">
       <c r="A10" s="2" t="s">
-        <v>841</v>
+        <v>800</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>842</v>
+        <v>801</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>844</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43">
       <c r="A11" s="2" t="s">
-        <v>845</v>
+        <v>804</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>846</v>
+        <v>805</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>847</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="57">
       <c r="A12" s="2" t="s">
-        <v>848</v>
+        <v>807</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>849</v>
+        <v>808</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>850</v>
+        <v>809</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>851</v>
+        <v>810</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29">
       <c r="A13" s="2" t="s">
-        <v>852</v>
+        <v>811</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>853</v>
+        <v>812</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>854</v>
+        <v>813</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>855</v>
+        <v>814</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>856</v>
+        <v>815</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>857</v>
+        <v>816</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>858</v>
+        <v>817</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>859</v>
+        <v>818</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="29">
       <c r="A15" s="2" t="s">
-        <v>860</v>
+        <v>819</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>861</v>
+        <v>820</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>862</v>
+        <v>821</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>863</v>
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>864</v>
+        <v>823</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>865</v>
+        <v>824</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>866</v>
+        <v>825</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>867</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="43">
       <c r="A17" s="2" t="s">
-        <v>868</v>
+        <v>827</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>869</v>
+        <v>828</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>870</v>
+        <v>829</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>871</v>
+        <v>830</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>872</v>
+        <v>831</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>873</v>
+        <v>832</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>874</v>
+        <v>833</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>875</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="43">
       <c r="A19" s="2" t="s">
-        <v>876</v>
+        <v>835</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>877</v>
+        <v>836</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>878</v>
+        <v>837</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>879</v>
+        <v>838</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>880</v>
+        <v>839</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>881</v>
+        <v>840</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>882</v>
+        <v>841</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>883</v>
+        <v>842</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>884</v>
+        <v>843</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="57">
       <c r="A22" s="2" t="s">
-        <v>885</v>
+        <v>844</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>886</v>
+        <v>845</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>887</v>
+        <v>846</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>888</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>889</v>
+        <v>848</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>890</v>
+        <v>849</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>891</v>
+        <v>850</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>892</v>
+        <v>851</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="43">
       <c r="A24" s="2" t="s">
-        <v>893</v>
+        <v>852</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>894</v>
+        <v>853</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>895</v>
+        <v>854</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>896</v>
+        <v>855</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>897</v>
+        <v>856</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>898</v>
+        <v>857</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>899</v>
+        <v>858</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>900</v>
+        <v>859</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="43">
       <c r="A26" s="2" t="s">
-        <v>901</v>
+        <v>860</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>902</v>
+        <v>861</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>903</v>
+        <v>862</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>904</v>
+        <v>863</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>906</v>
+        <v>865</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>907</v>
+        <v>866</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>908</v>
+        <v>867</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="57">
       <c r="A28" s="2" t="s">
-        <v>909</v>
+        <v>868</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>910</v>
+        <v>869</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>911</v>
+        <v>870</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>912</v>
+        <v>871</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>913</v>
+        <v>872</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>830</v>
+        <v>789</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>914</v>
+        <v>873</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>832</v>
+        <v>791</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>915</v>
+        <v>874</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>916</v>
+        <v>875</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>917</v>
+        <v>876</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>918</v>
+        <v>877</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>919</v>
+        <v>878</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>920</v>
+        <v>879</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>920</v>
+        <v>879</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>920</v>
+        <v>879</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>921</v>
+        <v>880</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>922</v>
+        <v>881</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>923</v>
+        <v>882</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>924</v>
+        <v>883</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>925</v>
+        <v>884</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>926</v>
+        <v>885</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>926</v>
+        <v>885</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>926</v>
+        <v>885</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>927</v>
+        <v>886</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>928</v>
+        <v>887</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>929</v>
+        <v>888</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>930</v>
+        <v>889</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>931</v>
+        <v>890</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>932</v>
+        <v>891</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>933</v>
+        <v>892</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>934</v>
+        <v>893</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>935</v>
+        <v>894</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>936</v>
+        <v>895</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>937</v>
+        <v>896</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>938</v>
+        <v>897</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>939</v>
+        <v>898</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>940</v>
+        <v>899</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>604</v>
+        <v>563</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>605</v>
+        <v>564</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>941</v>
+        <v>900</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>604</v>
+        <v>563</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>940</v>
+        <v>899</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>942</v>
+        <v>901</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>943</v>
+        <v>902</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>944</v>
+        <v>903</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>945</v>
+        <v>904</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>946</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>947</v>
+        <v>906</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>948</v>
+        <v>907</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>949</v>
+        <v>908</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>950</v>
+        <v>909</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>951</v>
+        <v>910</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>952</v>
+        <v>911</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>953</v>
+        <v>912</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>954</v>
+        <v>913</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>955</v>
+        <v>914</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>628</v>
+        <v>587</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>956</v>
+        <v>915</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>957</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>958</v>
+        <v>917</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>636</v>
+        <v>595</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>637</v>
+        <v>596</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>959</v>
+        <v>918</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>960</v>
+        <v>919</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>961</v>
+        <v>920</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>962</v>
+        <v>921</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>963</v>
+        <v>922</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>964</v>
+        <v>923</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>964</v>
+        <v>923</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>964</v>
+        <v>923</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>965</v>
+        <v>924</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>967</v>
+        <v>926</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>967</v>
+        <v>926</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>968</v>
+        <v>927</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>969</v>
+        <v>928</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>970</v>
+        <v>929</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>971</v>
+        <v>930</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>972</v>
+        <v>931</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>973</v>
+        <v>932</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>974</v>
+        <v>933</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>975</v>
+        <v>934</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>976</v>
+        <v>935</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>977</v>
+        <v>936</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>978</v>
+        <v>937</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="113">
       <c r="A50" s="2" t="s">
-        <v>979</v>
+        <v>938</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>980</v>
+        <v>939</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>981</v>
+        <v>940</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>982</v>
+        <v>941</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>983</v>
+        <v>942</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>984</v>
+        <v>943</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>985</v>
+        <v>944</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>986</v>
+        <v>945</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>987</v>
+        <v>946</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>988</v>
+        <v>947</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>989</v>
+        <v>948</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>990</v>
+        <v>949</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>991</v>
+        <v>950</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="113">
       <c r="A54" s="2" t="s">
-        <v>992</v>
+        <v>951</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>993</v>
+        <v>952</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>994</v>
+        <v>953</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>995</v>
+        <v>954</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="29">
       <c r="A55" s="2" t="s">
-        <v>996</v>
+        <v>955</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>997</v>
+        <v>956</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>998</v>
+        <v>957</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>999</v>
+        <v>958</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>1000</v>
+        <v>959</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>1001</v>
+        <v>960</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1002</v>
+        <v>961</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1003</v>
+        <v>962</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1004</v>
+        <v>963</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="85">
       <c r="A58" s="2" t="s">
-        <v>1005</v>
+        <v>964</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1006</v>
+        <v>965</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1007</v>
+        <v>966</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1008</v>
+        <v>967</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>1009</v>
+        <v>968</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1010</v>
+        <v>969</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1011</v>
+        <v>970</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1012</v>
+        <v>971</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>1013</v>
+        <v>972</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1014</v>
+        <v>973</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1015</v>
+        <v>974</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1016</v>
+        <v>975</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="29">
       <c r="A61" s="2" t="s">
-        <v>1017</v>
+        <v>976</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1018</v>
+        <v>977</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1019</v>
+        <v>978</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1020</v>
+        <v>979</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>1021</v>
+        <v>980</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>722</v>
+        <v>681</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1022</v>
+        <v>981</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1023</v>
+        <v>982</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>1024</v>
+        <v>983</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1025</v>
+        <v>984</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1026</v>
+        <v>985</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1027</v>
+        <v>986</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="99">
       <c r="A64" s="2" t="s">
-        <v>1028</v>
+        <v>987</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1029</v>
+        <v>988</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1030</v>
+        <v>989</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1031</v>
+        <v>990</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>1032</v>
+        <v>991</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1033</v>
+        <v>992</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1034</v>
+        <v>993</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1035</v>
+        <v>994</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>1036</v>
+        <v>995</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>795</v>
+        <v>754</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>796</v>
+        <v>755</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>797</v>
+        <v>756</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>1037</v>
+        <v>996</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1038</v>
+        <v>997</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1039</v>
+        <v>998</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1040</v>
+        <v>999</v>
       </c>
     </row>
   </sheetData>
@@ -8754,982 +8981,982 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>1041</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1042</v>
+        <v>1001</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1043</v>
+        <v>1002</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1044</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>1045</v>
+        <v>1004</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1046</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>820</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>1047</v>
+        <v>1006</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1048</v>
+        <v>1007</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1049</v>
+        <v>1008</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1050</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>1051</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1052</v>
+        <v>1011</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1053</v>
+        <v>1012</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1054</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>1055</v>
+        <v>1014</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1056</v>
+        <v>1015</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1057</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1058</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>1059</v>
+        <v>1018</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1060</v>
+        <v>1019</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1060</v>
+        <v>1019</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1061</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>1062</v>
+        <v>1021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1063</v>
+        <v>1022</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1064</v>
+        <v>1023</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1065</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="43">
       <c r="A9" s="2" t="s">
-        <v>1066</v>
+        <v>1025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1067</v>
+        <v>1026</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1068</v>
+        <v>1027</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1069</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29">
       <c r="A10" s="2" t="s">
-        <v>1070</v>
+        <v>1029</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1071</v>
+        <v>1030</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1072</v>
+        <v>1031</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1073</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29">
       <c r="A11" s="2" t="s">
-        <v>1074</v>
+        <v>1033</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="43">
       <c r="A12" s="2" t="s">
-        <v>1075</v>
+        <v>1034</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1076</v>
+        <v>1035</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29">
       <c r="A13" s="2" t="s">
-        <v>1077</v>
+        <v>1036</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1078</v>
+        <v>1037</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1079</v>
+        <v>1038</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1080</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="29">
       <c r="A14" s="2" t="s">
-        <v>1081</v>
+        <v>1040</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1082</v>
+        <v>1041</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1083</v>
+        <v>1042</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1084</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>1085</v>
+        <v>1044</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1086</v>
+        <v>1045</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1087</v>
+        <v>1046</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1088</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="29">
       <c r="A16" s="2" t="s">
-        <v>1089</v>
+        <v>1048</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1090</v>
+        <v>1049</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1091</v>
+        <v>1050</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1092</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>1093</v>
+        <v>1052</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1094</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1095</v>
+        <v>1054</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1096</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="29">
       <c r="A18" s="2" t="s">
-        <v>1097</v>
+        <v>1056</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1098</v>
+        <v>1057</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1099</v>
+        <v>1058</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1100</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>1101</v>
+        <v>1060</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1103</v>
+        <v>1062</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1104</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="29">
       <c r="A20" s="2" t="s">
-        <v>1105</v>
+        <v>1064</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1106</v>
+        <v>1065</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1107</v>
+        <v>1066</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1108</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>1109</v>
+        <v>1068</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1110</v>
+        <v>1069</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1111</v>
+        <v>1070</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1112</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="57">
       <c r="A22" s="2" t="s">
-        <v>1113</v>
+        <v>1072</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1114</v>
+        <v>1073</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1115</v>
+        <v>1074</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1116</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>1117</v>
+        <v>1076</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1118</v>
+        <v>1077</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1119</v>
+        <v>1078</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1120</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="29">
       <c r="A24" s="2" t="s">
-        <v>1121</v>
+        <v>1080</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1122</v>
+        <v>1081</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1123</v>
+        <v>1082</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1124</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>1125</v>
+        <v>1084</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1126</v>
+        <v>1085</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1127</v>
+        <v>1086</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1128</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="29">
       <c r="A26" s="2" t="s">
-        <v>1129</v>
+        <v>1088</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1130</v>
+        <v>1089</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1131</v>
+        <v>1090</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1132</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>1133</v>
+        <v>1092</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1134</v>
+        <v>1093</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1135</v>
+        <v>1094</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1136</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="29">
       <c r="A28" s="2" t="s">
-        <v>1137</v>
+        <v>1096</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1138</v>
+        <v>1097</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1139</v>
+        <v>1098</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1140</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>1141</v>
+        <v>1100</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1142</v>
+        <v>1101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1143</v>
+        <v>1102</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1144</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>1145</v>
+        <v>1104</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1146</v>
+        <v>1105</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1147</v>
+        <v>1106</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1148</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="29">
       <c r="A31" s="2" t="s">
-        <v>1149</v>
+        <v>1108</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1150</v>
+        <v>1109</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1151</v>
+        <v>1110</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1152</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>1153</v>
+        <v>1112</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1154</v>
+        <v>1113</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1155</v>
+        <v>1114</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1156</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="43">
       <c r="A33" s="2" t="s">
-        <v>1157</v>
+        <v>1116</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1158</v>
+        <v>1117</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1159</v>
+        <v>1118</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1160</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>1161</v>
+        <v>1120</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1162</v>
+        <v>1121</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1163</v>
+        <v>1122</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1164</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="43">
       <c r="A35" s="2" t="s">
-        <v>1165</v>
+        <v>1124</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1166</v>
+        <v>1125</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1167</v>
+        <v>1126</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1168</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>1169</v>
+        <v>1128</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>932</v>
+        <v>891</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1170</v>
+        <v>1129</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1171</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>1172</v>
+        <v>1131</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>598</v>
+        <v>557</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>598</v>
+        <v>557</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>599</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>1173</v>
+        <v>1132</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1174</v>
+        <v>1133</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1175</v>
+        <v>1134</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1176</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>1177</v>
+        <v>1136</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1178</v>
+        <v>1137</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1178</v>
+        <v>1137</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1179</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>1180</v>
+        <v>1139</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1181</v>
+        <v>1140</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1182</v>
+        <v>1141</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1183</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>1184</v>
+        <v>1143</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1185</v>
+        <v>1144</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1185</v>
+        <v>1144</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1185</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>1186</v>
+        <v>1145</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1187</v>
+        <v>1146</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1188</v>
+        <v>1147</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1189</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>1190</v>
+        <v>1149</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1191</v>
+        <v>1150</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1192</v>
+        <v>1151</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1193</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>1194</v>
+        <v>1153</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1195</v>
+        <v>1154</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1196</v>
+        <v>1155</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1197</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>1198</v>
+        <v>1157</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1199</v>
+        <v>1158</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1200</v>
+        <v>1159</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1201</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>1202</v>
+        <v>1161</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1203</v>
+        <v>1162</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1204</v>
+        <v>1163</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1203</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>1205</v>
+        <v>1164</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1206</v>
+        <v>1165</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>973</v>
+        <v>932</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>974</v>
+        <v>933</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>1207</v>
+        <v>1166</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1208</v>
+        <v>1167</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1209</v>
+        <v>1168</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1210</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="113">
       <c r="A49" s="2" t="s">
-        <v>1211</v>
+        <v>1170</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1212</v>
+        <v>1171</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1213</v>
+        <v>1172</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1214</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>1215</v>
+        <v>1174</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1216</v>
+        <v>1175</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1217</v>
+        <v>1176</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1218</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>1219</v>
+        <v>1178</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1220</v>
+        <v>1179</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1221</v>
+        <v>1180</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1222</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>1223</v>
+        <v>1182</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1224</v>
+        <v>1183</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1225</v>
+        <v>1184</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1226</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>1227</v>
+        <v>1186</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1228</v>
+        <v>1187</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1229</v>
+        <v>1188</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1230</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="57">
       <c r="A54" s="2" t="s">
-        <v>1231</v>
+        <v>1190</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1232</v>
+        <v>1191</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1233</v>
+        <v>1192</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1234</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="127">
       <c r="A55" s="2" t="s">
-        <v>1235</v>
+        <v>1194</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1236</v>
+        <v>1195</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1237</v>
+        <v>1196</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1238</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>1239</v>
+        <v>1198</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1240</v>
+        <v>1199</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1241</v>
+        <v>1200</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1242</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>1243</v>
+        <v>1202</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1244</v>
+        <v>1203</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1245</v>
+        <v>1204</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1246</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>1247</v>
+        <v>1206</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1249</v>
+        <v>1208</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1250</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="71">
       <c r="A59" s="2" t="s">
-        <v>1251</v>
+        <v>1210</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1252</v>
+        <v>1211</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1253</v>
+        <v>1212</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1254</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>1255</v>
+        <v>1214</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1256</v>
+        <v>1215</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1257</v>
+        <v>1216</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1258</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>1259</v>
+        <v>1218</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1260</v>
+        <v>1219</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1261</v>
+        <v>1220</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1262</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>1263</v>
+        <v>1222</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1264</v>
+        <v>1223</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1265</v>
+        <v>1224</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1266</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="99">
       <c r="A63" s="2" t="s">
-        <v>1267</v>
+        <v>1226</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1268</v>
+        <v>1227</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1269</v>
+        <v>1228</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1270</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>1271</v>
+        <v>1230</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1272</v>
+        <v>1231</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1272</v>
+        <v>1231</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1273</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>1274</v>
+        <v>1233</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1275</v>
+        <v>1234</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1277</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>1278</v>
+        <v>1237</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1279</v>
+        <v>1238</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1280</v>
+        <v>1239</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>1281</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="169">
       <c r="A67" s="2" t="s">
-        <v>1282</v>
+        <v>1241</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1283</v>
+        <v>1242</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1284</v>
+        <v>1243</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1285</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>1286</v>
+        <v>1245</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1287</v>
+        <v>1246</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1288</v>
+        <v>1247</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1289</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>1290</v>
+        <v>1249</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1291</v>
+        <v>1250</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1292</v>
+        <v>1251</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>1293</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>1294</v>
+        <v>1253</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1295</v>
+        <v>1254</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1296</v>
+        <v>1255</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1297</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>1298</v>
+        <v>1257</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1300</v>
+        <v>1259</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1301</v>
+        <v>1260</v>
       </c>
     </row>
   </sheetData>

--- a/translations/portfolio_translations_review_deduplicated.xlsx
+++ b/translations/portfolio_translations_review_deduplicated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anoukfontaine/Desktop/Portfolio/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF0FCAF-2560-3549-9C30-6BC1464347CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0215E80E-F633-4943-A17D-CE71392D9E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1880" yWindow="500" windowWidth="34200" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hero" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="1348">
   <si>
     <t>data-i18n</t>
   </si>
@@ -4047,6 +4047,30 @@
   </si>
   <si>
     <t>Remarque : Ce projet a été réalisé dans le cadre d'un emploi fixe. Afin de protéger les informations internes, les éléments propres à l’organisation ont été retirés et des données fictives ont été utilisées.</t>
+  </si>
+  <si>
+    <t>Gesamtverantwortung für das Projekt und das Produkt, vom UX/UI-Design über die Power-BI-Entwicklung und Einführung bis hin zur langfristigen Betreuung. Die dafür notwendigen Power-BI-Kenntnisse musste ich mir im Laufe des Projekts aneignen, was mit einer steilen Lernkurve verbunden war.</t>
+  </si>
+  <si>
+    <t>Zeitaufwändig</t>
+  </si>
+  <si>
+    <t>Datenanalysten verbrachten Tage damit, die Informationen aufzubereiten, bevor diese überhaupt gemeinsam mit Entscheidungsträgern analysiert und diskutiert werden konnten.</t>
+  </si>
+  <si>
+    <t>Eingeschränkte Datenexploration</t>
+  </si>
+  <si>
+    <t>Daten zu filtern, zu vergleichen oder zu untersuchen erforderte zusätzliche Übersichten und Berechnungen.</t>
+  </si>
+  <si>
+    <t>Niedriges Vertrauen in die Daten</t>
+  </si>
+  <si>
+    <t>Informationen waren über verschiedene Dokumente verteilt, und den Nutzer:innen war oft unklar, ob sie mit den aktuellsten und verlässlichsten Daten arbeiteten.</t>
+  </si>
+  <si>
+    <t>Alles in &lt;strong&gt;einem&lt;/strong&gt;.</t>
   </si>
 </sst>
 </file>
@@ -6029,6 +6053,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -6438,7 +6463,9 @@
       <c r="B21" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>1340</v>
+      </c>
       <c r="D21" s="2" t="s">
         <v>404</v>
       </c>
@@ -6454,7 +6481,9 @@
       <c r="B22" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>408</v>
+      </c>
       <c r="D22" s="2" t="s">
         <v>408</v>
       </c>
@@ -6470,7 +6499,9 @@
       <c r="B23" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>1341</v>
+      </c>
       <c r="D23" s="2" t="s">
         <v>412</v>
       </c>
@@ -6486,7 +6517,9 @@
       <c r="B24" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>1342</v>
+      </c>
       <c r="D24" s="2" t="s">
         <v>416</v>
       </c>
@@ -6502,7 +6535,9 @@
       <c r="B25" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>1343</v>
+      </c>
       <c r="D25" s="2" t="s">
         <v>420</v>
       </c>
@@ -6518,7 +6553,9 @@
       <c r="B26" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>1344</v>
+      </c>
       <c r="D26" s="2" t="s">
         <v>424</v>
       </c>
@@ -6534,7 +6571,9 @@
       <c r="B27" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>1345</v>
+      </c>
       <c r="D27" s="2" t="s">
         <v>428</v>
       </c>
@@ -6550,7 +6589,9 @@
       <c r="B28" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>1346</v>
+      </c>
       <c r="D28" s="2" t="s">
         <v>432</v>
       </c>
@@ -6566,7 +6607,9 @@
       <c r="B29" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>1347</v>
+      </c>
       <c r="D29" s="2" t="s">
         <v>436</v>
       </c>
